--- a/Result/checksun_type/橡膠.xlsx
+++ b/Result/checksun_type/橡膠.xlsx
@@ -641,62 +641,62 @@
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>my_signal</t>
+          <t>up_up</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_3d</t>
+          <t>up_up_3d</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_5d</t>
+          <t>up_up_5d</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>my_signal_10d</t>
+          <t>up_up_10d</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>up_up</t>
+          <t>bbw_cross</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>up_up_3d</t>
+          <t>MA_UP_d</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>up_up_5d</t>
+          <t>MA_UP_3d</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>up_up_10d</t>
+          <t>MA_UP_5d</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>bbw_cross</t>
+          <t>MA_UP_10d</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_3d</t>
+          <t>MA_UP_20d</t>
         </is>
       </c>
       <c r="BA1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_5d</t>
+          <t>MA_UP_30d</t>
         </is>
       </c>
       <c r="BB1" s="1" t="inlineStr">
         <is>
-          <t>MA_UP_10d</t>
+          <t>MA_UP_40d</t>
         </is>
       </c>
       <c r="BC1" s="1" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -1693,12 +1693,12 @@
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1893,11 +1893,15 @@
           <t>31.16</t>
         </is>
       </c>
-      <c r="CQ2" t="n">
-        <v>31.38</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>31.75</v>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>31.38</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>31.75</t>
+        </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
@@ -2650,7 +2654,7 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -2665,7 +2669,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -2675,12 +2679,12 @@
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -2875,11 +2879,15 @@
           <t>31.125</t>
         </is>
       </c>
-      <c r="CQ3" t="n">
-        <v>31.41</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>31.76</v>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>31.41</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>31.76</t>
+        </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
@@ -3647,7 +3655,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -3657,12 +3665,12 @@
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -3857,11 +3865,15 @@
           <t>31.115</t>
         </is>
       </c>
-      <c r="CQ4" t="n">
-        <v>31.45</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>31.79</v>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>31.45</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>31.79</t>
+        </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
@@ -4614,7 +4626,7 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
@@ -4629,7 +4641,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -4639,12 +4651,12 @@
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -4839,11 +4851,15 @@
           <t>31.125</t>
         </is>
       </c>
-      <c r="CQ5" t="n">
-        <v>31.52</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>31.8</v>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>31.52</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>31.8</t>
+        </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
@@ -5596,7 +5612,7 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
@@ -5611,7 +5627,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -5621,12 +5637,12 @@
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -5821,11 +5837,15 @@
           <t>31.195</t>
         </is>
       </c>
-      <c r="CQ6" t="n">
-        <v>31.61</v>
-      </c>
-      <c r="CR6" t="n">
-        <v>31.84</v>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>31.61</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>31.84</t>
+        </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
@@ -6578,7 +6598,7 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -6593,22 +6613,22 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -6803,11 +6823,15 @@
           <t>31.255</t>
         </is>
       </c>
-      <c r="CQ7" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>31.87</v>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>31.7</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>31.87</t>
+        </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
@@ -7560,7 +7584,7 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
@@ -7575,22 +7599,22 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -7785,11 +7809,15 @@
           <t>31.375</t>
         </is>
       </c>
-      <c r="CQ8" t="n">
-        <v>31.79</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>31.91</v>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>31.79</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
+          <t>31.91</t>
+        </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
@@ -8542,7 +8570,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -8557,22 +8585,22 @@
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -8767,11 +8795,15 @@
           <t>31.44</t>
         </is>
       </c>
-      <c r="CQ9" t="n">
-        <v>31.84</v>
-      </c>
-      <c r="CR9" t="n">
-        <v>31.93</v>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>31.84</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
+          <t>31.93</t>
+        </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
@@ -9524,7 +9556,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -9539,22 +9571,22 @@
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -9749,11 +9781,15 @@
           <t>31.52</t>
         </is>
       </c>
-      <c r="CQ10" t="n">
-        <v>31.92</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>31.96</v>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>31.92</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>31.96</t>
+        </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
@@ -10506,37 +10542,37 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -10731,11 +10767,15 @@
           <t>89.75</t>
         </is>
       </c>
-      <c r="CQ11" t="n">
-        <v>89.47</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>88.69</v>
+      <c r="CQ11" t="inlineStr">
+        <is>
+          <t>89.47</t>
+        </is>
+      </c>
+      <c r="CR11" t="inlineStr">
+        <is>
+          <t>88.69</t>
+        </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
@@ -10851,7 +10891,7 @@
       </c>
       <c r="DQ11" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR11" t="inlineStr">
@@ -11488,37 +11528,37 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -11713,11 +11753,15 @@
           <t>89.61</t>
         </is>
       </c>
-      <c r="CQ12" t="n">
-        <v>89.43000000000001</v>
-      </c>
-      <c r="CR12" t="n">
-        <v>88.64</v>
+      <c r="CQ12" t="inlineStr">
+        <is>
+          <t>89.43</t>
+        </is>
+      </c>
+      <c r="CR12" t="inlineStr">
+        <is>
+          <t>88.64</t>
+        </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
@@ -11833,7 +11877,7 @@
       </c>
       <c r="DQ12" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR12" t="inlineStr">
@@ -12470,37 +12514,37 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
@@ -12695,11 +12739,15 @@
           <t>89.47</t>
         </is>
       </c>
-      <c r="CQ13" t="n">
-        <v>89.40000000000001</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>88.59999999999999</v>
+      <c r="CQ13" t="inlineStr">
+        <is>
+          <t>89.4</t>
+        </is>
+      </c>
+      <c r="CR13" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
@@ -12815,7 +12863,7 @@
       </c>
       <c r="DQ13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR13" t="inlineStr">
@@ -13452,37 +13500,37 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
@@ -13677,11 +13725,15 @@
           <t>89.35999999999999</t>
         </is>
       </c>
-      <c r="CQ14" t="n">
-        <v>89.36</v>
-      </c>
-      <c r="CR14" t="n">
-        <v>88.56</v>
+      <c r="CQ14" t="inlineStr">
+        <is>
+          <t>89.36</t>
+        </is>
+      </c>
+      <c r="CR14" t="inlineStr">
+        <is>
+          <t>88.56</t>
+        </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
@@ -13797,7 +13849,7 @@
       </c>
       <c r="DQ14" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR14" t="inlineStr">
@@ -14434,37 +14486,37 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>17.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
@@ -14659,11 +14711,15 @@
           <t>89.31</t>
         </is>
       </c>
-      <c r="CQ15" t="n">
-        <v>89.33</v>
-      </c>
-      <c r="CR15" t="n">
-        <v>88.52</v>
+      <c r="CQ15" t="inlineStr">
+        <is>
+          <t>89.33</t>
+        </is>
+      </c>
+      <c r="CR15" t="inlineStr">
+        <is>
+          <t>88.52</t>
+        </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
@@ -14779,7 +14835,7 @@
       </c>
       <c r="DQ15" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR15" t="inlineStr">
@@ -15416,37 +15472,37 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
@@ -15641,11 +15697,15 @@
           <t>89.23</t>
         </is>
       </c>
-      <c r="CQ16" t="n">
-        <v>89.31999999999999</v>
-      </c>
-      <c r="CR16" t="n">
-        <v>88.51000000000001</v>
+      <c r="CQ16" t="inlineStr">
+        <is>
+          <t>89.32</t>
+        </is>
+      </c>
+      <c r="CR16" t="inlineStr">
+        <is>
+          <t>88.51</t>
+        </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
@@ -15761,7 +15821,7 @@
       </c>
       <c r="DQ16" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR16" t="inlineStr">
@@ -16398,37 +16458,37 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
@@ -16623,11 +16683,15 @@
           <t>89.21000000000001</t>
         </is>
       </c>
-      <c r="CQ17" t="n">
-        <v>89.3</v>
-      </c>
-      <c r="CR17" t="n">
-        <v>88.5</v>
+      <c r="CQ17" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="CR17" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
@@ -16743,7 +16807,7 @@
       </c>
       <c r="DQ17" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR17" t="inlineStr">
@@ -17380,7 +17444,7 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
@@ -17395,22 +17459,22 @@
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
@@ -17605,11 +17669,15 @@
           <t>89.22</t>
         </is>
       </c>
-      <c r="CQ18" t="n">
-        <v>89.23</v>
-      </c>
-      <c r="CR18" t="n">
-        <v>88.48</v>
+      <c r="CQ18" t="inlineStr">
+        <is>
+          <t>89.23</t>
+        </is>
+      </c>
+      <c r="CR18" t="inlineStr">
+        <is>
+          <t>88.48</t>
+        </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
@@ -18362,7 +18430,7 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
@@ -18377,22 +18445,22 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
@@ -18587,11 +18655,15 @@
           <t>89.24999999999999</t>
         </is>
       </c>
-      <c r="CQ19" t="n">
-        <v>89.17</v>
-      </c>
-      <c r="CR19" t="n">
-        <v>88.47</v>
+      <c r="CQ19" t="inlineStr">
+        <is>
+          <t>89.17</t>
+        </is>
+      </c>
+      <c r="CR19" t="inlineStr">
+        <is>
+          <t>88.47</t>
+        </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
@@ -19329,52 +19401,52 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT20" t="inlineStr">
+      <c r="AY20" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
@@ -19569,11 +19641,15 @@
           <t>14.64</t>
         </is>
       </c>
-      <c r="CQ20" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="CR20" t="n">
-        <v>14.66</v>
+      <c r="CQ20" t="inlineStr">
+        <is>
+          <t>14.72</t>
+        </is>
+      </c>
+      <c r="CR20" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
@@ -20311,52 +20387,52 @@
       </c>
       <c r="AS21" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT21" t="inlineStr">
+      <c r="AY21" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
@@ -20551,11 +20627,15 @@
           <t>14.675</t>
         </is>
       </c>
-      <c r="CQ21" t="n">
-        <v>14.74</v>
-      </c>
-      <c r="CR21" t="n">
-        <v>14.66</v>
+      <c r="CQ21" t="inlineStr">
+        <is>
+          <t>14.74</t>
+        </is>
+      </c>
+      <c r="CR21" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
@@ -21288,57 +21368,57 @@
       </c>
       <c r="AR22" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS22" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT22" t="inlineStr">
+      <c r="AY22" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
@@ -21533,11 +21613,15 @@
           <t>14.705</t>
         </is>
       </c>
-      <c r="CQ22" t="n">
-        <v>14.76</v>
-      </c>
-      <c r="CR22" t="n">
-        <v>14.66</v>
+      <c r="CQ22" t="inlineStr">
+        <is>
+          <t>14.76</t>
+        </is>
+      </c>
+      <c r="CR22" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
@@ -22270,57 +22354,57 @@
       </c>
       <c r="AR23" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS23" t="inlineStr">
+      <c r="AX23" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT23" t="inlineStr">
+      <c r="AY23" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
@@ -22515,11 +22599,15 @@
           <t>14.74</t>
         </is>
       </c>
-      <c r="CQ23" t="n">
-        <v>14.78</v>
-      </c>
-      <c r="CR23" t="n">
-        <v>14.67</v>
+      <c r="CQ23" t="inlineStr">
+        <is>
+          <t>14.78</t>
+        </is>
+      </c>
+      <c r="CR23" t="inlineStr">
+        <is>
+          <t>14.67</t>
+        </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
@@ -23247,62 +23335,62 @@
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AS24" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AT24" t="inlineStr">
+      <c r="AY24" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
@@ -23497,11 +23585,15 @@
           <t>14.775</t>
         </is>
       </c>
-      <c r="CQ24" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="CR24" t="n">
-        <v>14.67</v>
+      <c r="CQ24" t="inlineStr">
+        <is>
+          <t>14.8</t>
+        </is>
+      </c>
+      <c r="CR24" t="inlineStr">
+        <is>
+          <t>14.67</t>
+        </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
@@ -24254,7 +24346,7 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
@@ -24269,22 +24361,22 @@
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
@@ -24479,11 +24571,15 @@
           <t>14.75</t>
         </is>
       </c>
-      <c r="CQ25" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="CR25" t="n">
-        <v>14.67</v>
+      <c r="CQ25" t="inlineStr">
+        <is>
+          <t>14.79</t>
+        </is>
+      </c>
+      <c r="CR25" t="inlineStr">
+        <is>
+          <t>14.67</t>
+        </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
@@ -25236,7 +25332,7 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
@@ -25251,22 +25347,22 @@
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
@@ -25461,11 +25557,15 @@
           <t>14.755</t>
         </is>
       </c>
-      <c r="CQ26" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="CR26" t="n">
-        <v>14.67</v>
+      <c r="CQ26" t="inlineStr">
+        <is>
+          <t>14.79</t>
+        </is>
+      </c>
+      <c r="CR26" t="inlineStr">
+        <is>
+          <t>14.67</t>
+        </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
@@ -26218,7 +26318,7 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
@@ -26233,22 +26333,22 @@
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
@@ -26443,11 +26543,15 @@
           <t>14.77</t>
         </is>
       </c>
-      <c r="CQ27" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="CR27" t="n">
-        <v>14.66</v>
+      <c r="CQ27" t="inlineStr">
+        <is>
+          <t>14.79</t>
+        </is>
+      </c>
+      <c r="CR27" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
@@ -27200,7 +27304,7 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
@@ -27215,22 +27319,22 @@
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
@@ -27425,11 +27529,15 @@
           <t>14.785</t>
         </is>
       </c>
-      <c r="CQ28" t="n">
-        <v>14.79</v>
-      </c>
-      <c r="CR28" t="n">
-        <v>14.66</v>
+      <c r="CQ28" t="inlineStr">
+        <is>
+          <t>14.79</t>
+        </is>
+      </c>
+      <c r="CR28" t="inlineStr">
+        <is>
+          <t>14.66</t>
+        </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
@@ -28182,7 +28290,7 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
@@ -28197,7 +28305,7 @@
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
@@ -28207,12 +28315,12 @@
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
@@ -28407,11 +28515,15 @@
           <t>28.605</t>
         </is>
       </c>
-      <c r="CQ29" t="n">
-        <v>28.76</v>
-      </c>
-      <c r="CR29" t="n">
-        <v>28.98</v>
+      <c r="CQ29" t="inlineStr">
+        <is>
+          <t>28.76</t>
+        </is>
+      </c>
+      <c r="CR29" t="inlineStr">
+        <is>
+          <t>28.98</t>
+        </is>
       </c>
       <c r="CS29" t="inlineStr">
         <is>
@@ -29164,7 +29276,7 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
@@ -29179,7 +29291,7 @@
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
@@ -29189,12 +29301,12 @@
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
@@ -29389,11 +29501,15 @@
           <t>28.595</t>
         </is>
       </c>
-      <c r="CQ30" t="n">
-        <v>28.87</v>
-      </c>
-      <c r="CR30" t="n">
-        <v>28.97</v>
+      <c r="CQ30" t="inlineStr">
+        <is>
+          <t>28.87</t>
+        </is>
+      </c>
+      <c r="CR30" t="inlineStr">
+        <is>
+          <t>28.97</t>
+        </is>
       </c>
       <c r="CS30" t="inlineStr">
         <is>
@@ -30146,7 +30262,7 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
@@ -30161,22 +30277,22 @@
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
@@ -30371,11 +30487,15 @@
           <t>28.535</t>
         </is>
       </c>
-      <c r="CQ31" t="n">
-        <v>28.98</v>
-      </c>
-      <c r="CR31" t="n">
-        <v>28.97</v>
+      <c r="CQ31" t="inlineStr">
+        <is>
+          <t>28.98</t>
+        </is>
+      </c>
+      <c r="CR31" t="inlineStr">
+        <is>
+          <t>28.97</t>
+        </is>
       </c>
       <c r="CS31" t="inlineStr">
         <is>
@@ -31128,7 +31248,7 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
@@ -31143,22 +31263,22 @@
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
@@ -31353,11 +31473,15 @@
           <t>28.45</t>
         </is>
       </c>
-      <c r="CQ32" t="n">
-        <v>29.07</v>
-      </c>
-      <c r="CR32" t="n">
-        <v>28.94</v>
+      <c r="CQ32" t="inlineStr">
+        <is>
+          <t>29.07</t>
+        </is>
+      </c>
+      <c r="CR32" t="inlineStr">
+        <is>
+          <t>28.94</t>
+        </is>
       </c>
       <c r="CS32" t="inlineStr">
         <is>
@@ -32110,7 +32234,7 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
@@ -32125,22 +32249,22 @@
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
@@ -32335,11 +32459,15 @@
           <t>28.54</t>
         </is>
       </c>
-      <c r="CQ33" t="n">
-        <v>29.18</v>
-      </c>
-      <c r="CR33" t="n">
-        <v>28.94</v>
+      <c r="CQ33" t="inlineStr">
+        <is>
+          <t>29.18</t>
+        </is>
+      </c>
+      <c r="CR33" t="inlineStr">
+        <is>
+          <t>28.94</t>
+        </is>
       </c>
       <c r="CS33" t="inlineStr">
         <is>
@@ -33092,7 +33220,7 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
@@ -33107,22 +33235,22 @@
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
@@ -33317,11 +33445,15 @@
           <t>28.57</t>
         </is>
       </c>
-      <c r="CQ34" t="n">
-        <v>29.25</v>
-      </c>
-      <c r="CR34" t="n">
-        <v>28.93</v>
+      <c r="CQ34" t="inlineStr">
+        <is>
+          <t>29.25</t>
+        </is>
+      </c>
+      <c r="CR34" t="inlineStr">
+        <is>
+          <t>28.93</t>
+        </is>
       </c>
       <c r="CS34" t="inlineStr">
         <is>
@@ -34074,7 +34206,7 @@
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
@@ -34089,22 +34221,22 @@
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
@@ -34299,11 +34431,15 @@
           <t>28.645</t>
         </is>
       </c>
-      <c r="CQ35" t="n">
-        <v>29.35</v>
-      </c>
-      <c r="CR35" t="n">
-        <v>28.93</v>
+      <c r="CQ35" t="inlineStr">
+        <is>
+          <t>29.35</t>
+        </is>
+      </c>
+      <c r="CR35" t="inlineStr">
+        <is>
+          <t>28.93</t>
+        </is>
       </c>
       <c r="CS35" t="inlineStr">
         <is>
@@ -35056,7 +35192,7 @@
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
@@ -35071,22 +35207,22 @@
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
@@ -35281,11 +35417,15 @@
           <t>28.7</t>
         </is>
       </c>
-      <c r="CQ36" t="n">
-        <v>29.42</v>
-      </c>
-      <c r="CR36" t="n">
-        <v>28.92</v>
+      <c r="CQ36" t="inlineStr">
+        <is>
+          <t>29.42</t>
+        </is>
+      </c>
+      <c r="CR36" t="inlineStr">
+        <is>
+          <t>28.92</t>
+        </is>
       </c>
       <c r="CS36" t="inlineStr">
         <is>
@@ -36038,7 +36178,7 @@
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
@@ -36053,22 +36193,22 @@
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB37" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC37" t="inlineStr">
@@ -36263,11 +36403,15 @@
           <t>28.715</t>
         </is>
       </c>
-      <c r="CQ37" t="n">
-        <v>29.49</v>
-      </c>
-      <c r="CR37" t="n">
-        <v>28.92</v>
+      <c r="CQ37" t="inlineStr">
+        <is>
+          <t>29.49</t>
+        </is>
+      </c>
+      <c r="CR37" t="inlineStr">
+        <is>
+          <t>28.92</t>
+        </is>
       </c>
       <c r="CS37" t="inlineStr">
         <is>
@@ -37010,7 +37154,7 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
@@ -37020,12 +37164,12 @@
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -37035,22 +37179,22 @@
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
@@ -37245,11 +37389,15 @@
           <t>26.975</t>
         </is>
       </c>
-      <c r="CQ38" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR38" t="n">
-        <v>26.36</v>
+      <c r="CQ38" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR38" t="inlineStr">
+        <is>
+          <t>26.36</t>
+        </is>
       </c>
       <c r="CS38" t="inlineStr">
         <is>
@@ -37992,7 +38140,7 @@
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
@@ -38002,7 +38150,7 @@
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
@@ -38012,27 +38160,27 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
@@ -38227,11 +38375,15 @@
           <t>26.94</t>
         </is>
       </c>
-      <c r="CQ39" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR39" t="n">
-        <v>26.33</v>
+      <c r="CQ39" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR39" t="inlineStr">
+        <is>
+          <t>26.33</t>
+        </is>
       </c>
       <c r="CS39" t="inlineStr">
         <is>
@@ -38974,7 +39126,7 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU40" t="inlineStr">
@@ -38984,7 +39136,7 @@
       </c>
       <c r="AV40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW40" t="inlineStr">
@@ -38999,22 +39151,22 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
@@ -39209,11 +39361,15 @@
           <t>26.915</t>
         </is>
       </c>
-      <c r="CQ40" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR40" t="n">
-        <v>26.32</v>
+      <c r="CQ40" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR40" t="inlineStr">
+        <is>
+          <t>26.32</t>
+        </is>
       </c>
       <c r="CS40" t="inlineStr">
         <is>
@@ -39956,7 +40112,7 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU41" t="inlineStr">
@@ -39966,7 +40122,7 @@
       </c>
       <c r="AV41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW41" t="inlineStr">
@@ -39976,27 +40132,27 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB41" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC41" t="inlineStr">
@@ -40191,11 +40347,15 @@
           <t>26.875</t>
         </is>
       </c>
-      <c r="CQ41" t="n">
-        <v>26.85</v>
-      </c>
-      <c r="CR41" t="n">
-        <v>26.29</v>
+      <c r="CQ41" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="CR41" t="inlineStr">
+        <is>
+          <t>26.29</t>
+        </is>
       </c>
       <c r="CS41" t="inlineStr">
         <is>
@@ -40933,12 +41093,12 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
@@ -40948,7 +41108,7 @@
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
@@ -40958,27 +41118,27 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
@@ -41173,11 +41333,15 @@
           <t>26.87</t>
         </is>
       </c>
-      <c r="CQ42" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR42" t="n">
-        <v>26.27</v>
+      <c r="CQ42" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR42" t="inlineStr">
+        <is>
+          <t>26.27</t>
+        </is>
       </c>
       <c r="CS42" t="inlineStr">
         <is>
@@ -41915,12 +42079,12 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
@@ -41930,37 +42094,37 @@
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB43" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC43" t="inlineStr">
@@ -42155,11 +42319,15 @@
           <t>26.88</t>
         </is>
       </c>
-      <c r="CQ43" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR43" t="n">
-        <v>26.25</v>
+      <c r="CQ43" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR43" t="inlineStr">
+        <is>
+          <t>26.25</t>
+        </is>
       </c>
       <c r="CS43" t="inlineStr">
         <is>
@@ -42892,17 +43060,17 @@
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
@@ -42912,37 +43080,37 @@
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
@@ -43137,11 +43305,15 @@
           <t>26.88</t>
         </is>
       </c>
-      <c r="CQ44" t="n">
-        <v>26.86</v>
-      </c>
-      <c r="CR44" t="n">
-        <v>26.23</v>
+      <c r="CQ44" t="inlineStr">
+        <is>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="CR44" t="inlineStr">
+        <is>
+          <t>26.23</t>
+        </is>
       </c>
       <c r="CS44" t="inlineStr">
         <is>
@@ -43874,17 +44046,17 @@
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
@@ -43894,37 +44066,37 @@
       </c>
       <c r="AV45" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW45" t="inlineStr">
+      <c r="AX45" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
@@ -44119,11 +44291,15 @@
           <t>26.855</t>
         </is>
       </c>
-      <c r="CQ45" t="n">
-        <v>26.85</v>
-      </c>
-      <c r="CR45" t="n">
-        <v>26.21</v>
+      <c r="CQ45" t="inlineStr">
+        <is>
+          <t>26.85</t>
+        </is>
+      </c>
+      <c r="CR45" t="inlineStr">
+        <is>
+          <t>26.21</t>
+        </is>
       </c>
       <c r="CS45" t="inlineStr">
         <is>
@@ -44851,62 +45027,62 @@
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV46" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV46" t="inlineStr">
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW46" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
@@ -45101,11 +45277,15 @@
           <t>26.8</t>
         </is>
       </c>
-      <c r="CQ46" t="n">
-        <v>26.83</v>
-      </c>
-      <c r="CR46" t="n">
-        <v>26.19</v>
+      <c r="CQ46" t="inlineStr">
+        <is>
+          <t>26.83</t>
+        </is>
+      </c>
+      <c r="CR46" t="inlineStr">
+        <is>
+          <t>26.19</t>
+        </is>
       </c>
       <c r="CS46" t="inlineStr">
         <is>
@@ -45858,7 +46038,7 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
@@ -45873,7 +46053,7 @@
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
@@ -45888,7 +46068,7 @@
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
@@ -46083,11 +46263,15 @@
           <t>16.58</t>
         </is>
       </c>
-      <c r="CQ47" t="n">
-        <v>16.72</v>
-      </c>
-      <c r="CR47" t="n">
-        <v>17.36</v>
+      <c r="CQ47" t="inlineStr">
+        <is>
+          <t>16.72</t>
+        </is>
+      </c>
+      <c r="CR47" t="inlineStr">
+        <is>
+          <t>17.36</t>
+        </is>
       </c>
       <c r="CS47" t="inlineStr">
         <is>
@@ -46840,7 +47024,7 @@
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
@@ -46855,7 +47039,7 @@
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
@@ -46870,7 +47054,7 @@
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
@@ -47065,11 +47249,15 @@
           <t>16.565</t>
         </is>
       </c>
-      <c r="CQ48" t="n">
-        <v>16.76</v>
-      </c>
-      <c r="CR48" t="n">
-        <v>17.38</v>
+      <c r="CQ48" t="inlineStr">
+        <is>
+          <t>16.76</t>
+        </is>
+      </c>
+      <c r="CR48" t="inlineStr">
+        <is>
+          <t>17.38</t>
+        </is>
       </c>
       <c r="CS48" t="inlineStr">
         <is>
@@ -47822,7 +48010,7 @@
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
@@ -47837,7 +48025,7 @@
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
@@ -47852,7 +48040,7 @@
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
@@ -48047,11 +48235,15 @@
           <t>16.56</t>
         </is>
       </c>
-      <c r="CQ49" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="CR49" t="n">
-        <v>17.4</v>
+      <c r="CQ49" t="inlineStr">
+        <is>
+          <t>16.8</t>
+        </is>
+      </c>
+      <c r="CR49" t="inlineStr">
+        <is>
+          <t>17.4</t>
+        </is>
       </c>
       <c r="CS49" t="inlineStr">
         <is>
@@ -48804,7 +48996,7 @@
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
@@ -48819,7 +49011,7 @@
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
@@ -48834,7 +49026,7 @@
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
@@ -49029,11 +49221,15 @@
           <t>16.55</t>
         </is>
       </c>
-      <c r="CQ50" t="n">
-        <v>16.82</v>
-      </c>
-      <c r="CR50" t="n">
-        <v>17.43</v>
+      <c r="CQ50" t="inlineStr">
+        <is>
+          <t>16.82</t>
+        </is>
+      </c>
+      <c r="CR50" t="inlineStr">
+        <is>
+          <t>17.43</t>
+        </is>
       </c>
       <c r="CS50" t="inlineStr">
         <is>
@@ -49786,7 +49982,7 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
@@ -49801,7 +49997,7 @@
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
@@ -49816,7 +50012,7 @@
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
@@ -50011,11 +50207,15 @@
           <t>16.575</t>
         </is>
       </c>
-      <c r="CQ51" t="n">
-        <v>16.84</v>
-      </c>
-      <c r="CR51" t="n">
-        <v>17.46</v>
+      <c r="CQ51" t="inlineStr">
+        <is>
+          <t>16.84</t>
+        </is>
+      </c>
+      <c r="CR51" t="inlineStr">
+        <is>
+          <t>17.46</t>
+        </is>
       </c>
       <c r="CS51" t="inlineStr">
         <is>
@@ -50768,7 +50968,7 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -50783,7 +50983,7 @@
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
@@ -50798,7 +50998,7 @@
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
@@ -50993,11 +51193,15 @@
           <t>16.595</t>
         </is>
       </c>
-      <c r="CQ52" t="n">
-        <v>16.86</v>
-      </c>
-      <c r="CR52" t="n">
-        <v>17.5</v>
+      <c r="CQ52" t="inlineStr">
+        <is>
+          <t>16.86</t>
+        </is>
+      </c>
+      <c r="CR52" t="inlineStr">
+        <is>
+          <t>17.5</t>
+        </is>
       </c>
       <c r="CS52" t="inlineStr">
         <is>
@@ -51750,7 +51954,7 @@
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
@@ -51765,7 +51969,7 @@
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
@@ -51775,12 +51979,12 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
@@ -51975,11 +52179,15 @@
           <t>16.635</t>
         </is>
       </c>
-      <c r="CQ53" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="CR53" t="n">
-        <v>17.52</v>
+      <c r="CQ53" t="inlineStr">
+        <is>
+          <t>16.9</t>
+        </is>
+      </c>
+      <c r="CR53" t="inlineStr">
+        <is>
+          <t>17.52</t>
+        </is>
       </c>
       <c r="CS53" t="inlineStr">
         <is>
@@ -52732,7 +52940,7 @@
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
@@ -52747,7 +52955,7 @@
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
@@ -52757,12 +52965,12 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
@@ -52957,11 +53165,15 @@
           <t>16.685</t>
         </is>
       </c>
-      <c r="CQ54" t="n">
-        <v>16.93</v>
-      </c>
-      <c r="CR54" t="n">
-        <v>17.54</v>
+      <c r="CQ54" t="inlineStr">
+        <is>
+          <t>16.93</t>
+        </is>
+      </c>
+      <c r="CR54" t="inlineStr">
+        <is>
+          <t>17.54</t>
+        </is>
       </c>
       <c r="CS54" t="inlineStr">
         <is>
@@ -53714,7 +53926,7 @@
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -53729,7 +53941,7 @@
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
@@ -53739,12 +53951,12 @@
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
@@ -53939,11 +54151,15 @@
           <t>16.72</t>
         </is>
       </c>
-      <c r="CQ55" t="n">
-        <v>16.98</v>
-      </c>
-      <c r="CR55" t="n">
-        <v>17.56</v>
+      <c r="CQ55" t="inlineStr">
+        <is>
+          <t>16.98</t>
+        </is>
+      </c>
+      <c r="CR55" t="inlineStr">
+        <is>
+          <t>17.56</t>
+        </is>
       </c>
       <c r="CS55" t="inlineStr">
         <is>
@@ -54696,7 +54912,7 @@
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
@@ -54711,7 +54927,7 @@
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
@@ -54721,12 +54937,12 @@
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
@@ -54921,11 +55137,15 @@
           <t>30.21</t>
         </is>
       </c>
-      <c r="CQ56" t="n">
-        <v>30.34</v>
-      </c>
-      <c r="CR56" t="n">
-        <v>30.75</v>
+      <c r="CQ56" t="inlineStr">
+        <is>
+          <t>30.34</t>
+        </is>
+      </c>
+      <c r="CR56" t="inlineStr">
+        <is>
+          <t>30.75</t>
+        </is>
       </c>
       <c r="CS56" t="inlineStr">
         <is>
@@ -55678,7 +55898,7 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -55693,7 +55913,7 @@
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
@@ -55703,12 +55923,12 @@
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
@@ -55903,11 +56123,15 @@
           <t>30.155</t>
         </is>
       </c>
-      <c r="CQ57" t="n">
-        <v>30.37</v>
-      </c>
-      <c r="CR57" t="n">
-        <v>30.76</v>
+      <c r="CQ57" t="inlineStr">
+        <is>
+          <t>30.37</t>
+        </is>
+      </c>
+      <c r="CR57" t="inlineStr">
+        <is>
+          <t>30.76</t>
+        </is>
       </c>
       <c r="CS57" t="inlineStr">
         <is>
@@ -56660,7 +56884,7 @@
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
@@ -56675,7 +56899,7 @@
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
@@ -56685,12 +56909,12 @@
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
@@ -56885,11 +57109,15 @@
           <t>30.1</t>
         </is>
       </c>
-      <c r="CQ58" t="n">
-        <v>30.4</v>
-      </c>
-      <c r="CR58" t="n">
-        <v>30.8</v>
+      <c r="CQ58" t="inlineStr">
+        <is>
+          <t>30.4</t>
+        </is>
+      </c>
+      <c r="CR58" t="inlineStr">
+        <is>
+          <t>30.8</t>
+        </is>
       </c>
       <c r="CS58" t="inlineStr">
         <is>
@@ -57642,7 +57870,7 @@
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
@@ -57657,7 +57885,7 @@
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
@@ -57667,12 +57895,12 @@
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
@@ -57867,11 +58095,15 @@
           <t>30.05</t>
         </is>
       </c>
-      <c r="CQ59" t="n">
-        <v>30.41</v>
-      </c>
-      <c r="CR59" t="n">
-        <v>30.85</v>
+      <c r="CQ59" t="inlineStr">
+        <is>
+          <t>30.41</t>
+        </is>
+      </c>
+      <c r="CR59" t="inlineStr">
+        <is>
+          <t>30.85</t>
+        </is>
       </c>
       <c r="CS59" t="inlineStr">
         <is>
@@ -58624,7 +58856,7 @@
       </c>
       <c r="AV60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW60" t="inlineStr">
@@ -58639,7 +58871,7 @@
       </c>
       <c r="AY60" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ60" t="inlineStr">
@@ -58649,12 +58881,12 @@
       </c>
       <c r="BA60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB60" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC60" t="inlineStr">
@@ -58849,11 +59081,15 @@
           <t>30.08</t>
         </is>
       </c>
-      <c r="CQ60" t="n">
-        <v>30.44</v>
-      </c>
-      <c r="CR60" t="n">
-        <v>30.92</v>
+      <c r="CQ60" t="inlineStr">
+        <is>
+          <t>30.44</t>
+        </is>
+      </c>
+      <c r="CR60" t="inlineStr">
+        <is>
+          <t>30.92</t>
+        </is>
       </c>
       <c r="CS60" t="inlineStr">
         <is>
@@ -59606,7 +59842,7 @@
       </c>
       <c r="AV61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW61" t="inlineStr">
@@ -59621,7 +59857,7 @@
       </c>
       <c r="AY61" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ61" t="inlineStr">
@@ -59631,12 +59867,12 @@
       </c>
       <c r="BA61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC61" t="inlineStr">
@@ -59831,11 +60067,15 @@
           <t>30.13</t>
         </is>
       </c>
-      <c r="CQ61" t="n">
-        <v>30.48</v>
-      </c>
-      <c r="CR61" t="n">
-        <v>30.99</v>
+      <c r="CQ61" t="inlineStr">
+        <is>
+          <t>30.48</t>
+        </is>
+      </c>
+      <c r="CR61" t="inlineStr">
+        <is>
+          <t>30.99</t>
+        </is>
       </c>
       <c r="CS61" t="inlineStr">
         <is>
@@ -60588,7 +60828,7 @@
       </c>
       <c r="AV62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW62" t="inlineStr">
@@ -60603,22 +60843,22 @@
       </c>
       <c r="AY62" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB62" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC62" t="inlineStr">
@@ -60813,11 +61053,15 @@
           <t>30.2</t>
         </is>
       </c>
-      <c r="CQ62" t="n">
-        <v>30.55</v>
-      </c>
-      <c r="CR62" t="n">
-        <v>31.04</v>
+      <c r="CQ62" t="inlineStr">
+        <is>
+          <t>30.55</t>
+        </is>
+      </c>
+      <c r="CR62" t="inlineStr">
+        <is>
+          <t>31.04</t>
+        </is>
       </c>
       <c r="CS62" t="inlineStr">
         <is>
@@ -61570,7 +61814,7 @@
       </c>
       <c r="AV63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW63" t="inlineStr">
@@ -61585,22 +61829,22 @@
       </c>
       <c r="AY63" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB63" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC63" t="inlineStr">
@@ -61795,11 +62039,15 @@
           <t>30.26</t>
         </is>
       </c>
-      <c r="CQ63" t="n">
-        <v>30.62</v>
-      </c>
-      <c r="CR63" t="n">
-        <v>31.1</v>
+      <c r="CQ63" t="inlineStr">
+        <is>
+          <t>30.62</t>
+        </is>
+      </c>
+      <c r="CR63" t="inlineStr">
+        <is>
+          <t>31.1</t>
+        </is>
       </c>
       <c r="CS63" t="inlineStr">
         <is>
@@ -62552,7 +62800,7 @@
       </c>
       <c r="AV64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW64" t="inlineStr">
@@ -62567,22 +62815,22 @@
       </c>
       <c r="AY64" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BB64" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC64" t="inlineStr">
@@ -62777,11 +63025,15 @@
           <t>30.325</t>
         </is>
       </c>
-      <c r="CQ64" t="n">
-        <v>30.69</v>
-      </c>
-      <c r="CR64" t="n">
-        <v>31.15</v>
+      <c r="CQ64" t="inlineStr">
+        <is>
+          <t>30.69</t>
+        </is>
+      </c>
+      <c r="CR64" t="inlineStr">
+        <is>
+          <t>31.15</t>
+        </is>
       </c>
       <c r="CS64" t="inlineStr">
         <is>
@@ -63509,62 +63761,62 @@
       </c>
       <c r="AQ65" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AS65" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AT65" t="inlineStr">
-        <is>
-          <t>7.0</t>
-        </is>
-      </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB65" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC65" t="inlineStr">
@@ -63759,11 +64011,15 @@
           <t>10.915</t>
         </is>
       </c>
-      <c r="CQ65" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="CR65" t="n">
-        <v>10.37</v>
+      <c r="CQ65" t="inlineStr">
+        <is>
+          <t>10.64</t>
+        </is>
+      </c>
+      <c r="CR65" t="inlineStr">
+        <is>
+          <t>10.37</t>
+        </is>
       </c>
       <c r="CS65" t="inlineStr">
         <is>
@@ -63879,7 +64135,7 @@
       </c>
       <c r="DQ65" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR65" t="inlineStr">
@@ -64491,62 +64747,62 @@
       </c>
       <c r="AQ66" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR66" t="inlineStr">
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS66" t="inlineStr">
+      <c r="AX66" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT66" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV66" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW66" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AY66" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BB66" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="BC66" t="inlineStr">
@@ -64741,11 +64997,15 @@
           <t>10.86</t>
         </is>
       </c>
-      <c r="CQ66" t="n">
-        <v>10.62</v>
-      </c>
-      <c r="CR66" t="n">
-        <v>10.36</v>
+      <c r="CQ66" t="inlineStr">
+        <is>
+          <t>10.62</t>
+        </is>
+      </c>
+      <c r="CR66" t="inlineStr">
+        <is>
+          <t>10.36</t>
+        </is>
       </c>
       <c r="CS66" t="inlineStr">
         <is>
@@ -64861,7 +65121,7 @@
       </c>
       <c r="DQ66" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR66" t="inlineStr">
@@ -65473,62 +65733,62 @@
       </c>
       <c r="AQ67" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR67" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS67" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AT67" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR67" t="inlineStr">
+      <c r="AV67" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW67" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS67" t="inlineStr">
+      <c r="AX67" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="AT67" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV67" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW67" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AY67" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB67" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC67" t="inlineStr">
@@ -65723,11 +65983,15 @@
           <t>10.79</t>
         </is>
       </c>
-      <c r="CQ67" t="n">
-        <v>10.59</v>
-      </c>
-      <c r="CR67" t="n">
-        <v>10.35</v>
+      <c r="CQ67" t="inlineStr">
+        <is>
+          <t>10.59</t>
+        </is>
+      </c>
+      <c r="CR67" t="inlineStr">
+        <is>
+          <t>10.35</t>
+        </is>
       </c>
       <c r="CS67" t="inlineStr">
         <is>
@@ -65843,7 +66107,7 @@
       </c>
       <c r="DQ67" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR67" t="inlineStr">
@@ -66455,62 +66719,62 @@
       </c>
       <c r="AQ68" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR68" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AS68" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT68" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR68" t="inlineStr">
+      <c r="AV68" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW68" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS68" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AT68" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV68" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB68" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BC68" t="inlineStr">
@@ -66705,11 +66969,15 @@
           <t>10.705</t>
         </is>
       </c>
-      <c r="CQ68" t="n">
-        <v>10.55</v>
-      </c>
-      <c r="CR68" t="n">
-        <v>10.33</v>
+      <c r="CQ68" t="inlineStr">
+        <is>
+          <t>10.55</t>
+        </is>
+      </c>
+      <c r="CR68" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
       </c>
       <c r="CS68" t="inlineStr">
         <is>
@@ -66825,7 +67093,7 @@
       </c>
       <c r="DQ68" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR68" t="inlineStr">
@@ -67437,62 +67705,62 @@
       </c>
       <c r="AQ69" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR69" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="AS69" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AT69" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR69" t="inlineStr">
+      <c r="AV69" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AW69" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AS69" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AT69" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AV69" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB69" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BC69" t="inlineStr">
@@ -67687,11 +67955,15 @@
           <t>10.685</t>
         </is>
       </c>
-      <c r="CQ69" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="CR69" t="n">
-        <v>10.33</v>
+      <c r="CQ69" t="inlineStr">
+        <is>
+          <t>10.53</t>
+        </is>
+      </c>
+      <c r="CR69" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
       </c>
       <c r="CS69" t="inlineStr">
         <is>
@@ -67807,7 +68079,7 @@
       </c>
       <c r="DQ69" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR69" t="inlineStr">
@@ -68419,32 +68691,32 @@
       </c>
       <c r="AQ70" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AR70" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="AS70" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="AT70" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AS70" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr">
-        <is>
-          <t>2.0</t>
-        </is>
-      </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AV70" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AW70" t="inlineStr">
@@ -68459,22 +68731,22 @@
       </c>
       <c r="AY70" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB70" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BC70" t="inlineStr">
@@ -68669,11 +68941,15 @@
           <t>10.63</t>
         </is>
       </c>
-      <c r="CQ70" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="CR70" t="n">
-        <v>10.33</v>
+      <c r="CQ70" t="inlineStr">
+        <is>
+          <t>10.5</t>
+        </is>
+      </c>
+      <c r="CR70" t="inlineStr">
+        <is>
+          <t>10.33</t>
+        </is>
       </c>
       <c r="CS70" t="inlineStr">
         <is>
@@ -68789,7 +69065,7 @@
       </c>
       <c r="DQ70" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR70" t="inlineStr">
@@ -69406,57 +69682,57 @@
       </c>
       <c r="AR71" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AU71" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV71" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV71" t="inlineStr">
+      <c r="AW71" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW71" t="inlineStr">
+      <c r="AX71" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>5.0</t>
-        </is>
-      </c>
       <c r="AY71" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB71" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BC71" t="inlineStr">
@@ -69651,11 +69927,15 @@
           <t>10.545</t>
         </is>
       </c>
-      <c r="CQ71" t="n">
-        <v>10.44</v>
-      </c>
-      <c r="CR71" t="n">
-        <v>10.31</v>
+      <c r="CQ71" t="inlineStr">
+        <is>
+          <t>10.44</t>
+        </is>
+      </c>
+      <c r="CR71" t="inlineStr">
+        <is>
+          <t>10.31</t>
+        </is>
       </c>
       <c r="CS71" t="inlineStr">
         <is>
@@ -69771,7 +70051,7 @@
       </c>
       <c r="DQ71" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR71" t="inlineStr">
@@ -70383,62 +70663,62 @@
       </c>
       <c r="AQ72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AR72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AU72" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AV72" t="inlineStr">
+        <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AV72" t="inlineStr">
+      <c r="AW72" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AW72" t="inlineStr">
+      <c r="AX72" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>4.0</t>
-        </is>
-      </c>
       <c r="AY72" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB72" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BC72" t="inlineStr">
@@ -70633,11 +70913,15 @@
           <t>10.495</t>
         </is>
       </c>
-      <c r="CQ72" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="CR72" t="n">
-        <v>10.3</v>
+      <c r="CQ72" t="inlineStr">
+        <is>
+          <t>10.42</t>
+        </is>
+      </c>
+      <c r="CR72" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
       </c>
       <c r="CS72" t="inlineStr">
         <is>
@@ -70753,7 +71037,7 @@
       </c>
       <c r="DQ72" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR72" t="inlineStr">
@@ -71370,17 +71654,17 @@
       </c>
       <c r="AR73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AU73" t="inlineStr">
@@ -71390,37 +71674,37 @@
       </c>
       <c r="AV73" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AW73" t="inlineStr">
+      <c r="AX73" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>3.0</t>
-        </is>
-      </c>
       <c r="AY73" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB73" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BC73" t="inlineStr">
@@ -71615,11 +71899,15 @@
           <t>10.44</t>
         </is>
       </c>
-      <c r="CQ73" t="n">
-        <v>10.41</v>
-      </c>
-      <c r="CR73" t="n">
-        <v>10.3</v>
+      <c r="CQ73" t="inlineStr">
+        <is>
+          <t>10.41</t>
+        </is>
+      </c>
+      <c r="CR73" t="inlineStr">
+        <is>
+          <t>10.3</t>
+        </is>
       </c>
       <c r="CS73" t="inlineStr">
         <is>
@@ -71735,7 +72023,7 @@
       </c>
       <c r="DQ73" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR73" t="inlineStr">
@@ -72367,12 +72655,12 @@
       </c>
       <c r="AU74" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW74" t="inlineStr">
@@ -72387,22 +72675,22 @@
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC74" t="inlineStr">
@@ -72597,11 +72885,15 @@
           <t>27.82999999999999</t>
         </is>
       </c>
-      <c r="CQ74" t="n">
-        <v>27.19</v>
-      </c>
-      <c r="CR74" t="n">
-        <v>26.26</v>
+      <c r="CQ74" t="inlineStr">
+        <is>
+          <t>27.19</t>
+        </is>
+      </c>
+      <c r="CR74" t="inlineStr">
+        <is>
+          <t>26.26</t>
+        </is>
       </c>
       <c r="CS74" t="inlineStr">
         <is>
@@ -72717,7 +73009,7 @@
       </c>
       <c r="DQ74" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR74" t="inlineStr">
@@ -73349,12 +73641,12 @@
       </c>
       <c r="AU75" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW75" t="inlineStr">
@@ -73369,22 +73661,22 @@
       </c>
       <c r="AY75" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC75" t="inlineStr">
@@ -73579,11 +73871,15 @@
           <t>27.7</t>
         </is>
       </c>
-      <c r="CQ75" t="n">
-        <v>27.2</v>
-      </c>
-      <c r="CR75" t="n">
-        <v>26.18</v>
+      <c r="CQ75" t="inlineStr">
+        <is>
+          <t>27.2</t>
+        </is>
+      </c>
+      <c r="CR75" t="inlineStr">
+        <is>
+          <t>26.18</t>
+        </is>
       </c>
       <c r="CS75" t="inlineStr">
         <is>
@@ -73699,7 +73995,7 @@
       </c>
       <c r="DQ75" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR75" t="inlineStr">
@@ -74331,12 +74627,12 @@
       </c>
       <c r="AU76" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AV76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW76" t="inlineStr">
@@ -74351,22 +74647,22 @@
       </c>
       <c r="AY76" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC76" t="inlineStr">
@@ -74561,11 +74857,15 @@
           <t>27.48</t>
         </is>
       </c>
-      <c r="CQ76" t="n">
-        <v>27.24</v>
-      </c>
-      <c r="CR76" t="n">
-        <v>26.1</v>
+      <c r="CQ76" t="inlineStr">
+        <is>
+          <t>27.24</t>
+        </is>
+      </c>
+      <c r="CR76" t="inlineStr">
+        <is>
+          <t>26.1</t>
+        </is>
       </c>
       <c r="CS76" t="inlineStr">
         <is>
@@ -74681,7 +74981,7 @@
       </c>
       <c r="DQ76" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="DR76" t="inlineStr">
@@ -75318,7 +75618,7 @@
       </c>
       <c r="AV77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW77" t="inlineStr">
@@ -75333,22 +75633,22 @@
       </c>
       <c r="AY77" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB77" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC77" t="inlineStr">
@@ -75543,11 +75843,15 @@
           <t>27.21</t>
         </is>
       </c>
-      <c r="CQ77" t="n">
-        <v>27.25</v>
-      </c>
-      <c r="CR77" t="n">
-        <v>26</v>
+      <c r="CQ77" t="inlineStr">
+        <is>
+          <t>27.25</t>
+        </is>
+      </c>
+      <c r="CR77" t="inlineStr">
+        <is>
+          <t>26.0</t>
+        </is>
       </c>
       <c r="CS77" t="inlineStr">
         <is>
@@ -76300,7 +76604,7 @@
       </c>
       <c r="AV78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW78" t="inlineStr">
@@ -76315,22 +76619,22 @@
       </c>
       <c r="AY78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC78" t="inlineStr">
@@ -76525,11 +76829,15 @@
           <t>27.045</t>
         </is>
       </c>
-      <c r="CQ78" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="CR78" t="n">
-        <v>25.92</v>
+      <c r="CQ78" t="inlineStr">
+        <is>
+          <t>27.29</t>
+        </is>
+      </c>
+      <c r="CR78" t="inlineStr">
+        <is>
+          <t>25.92</t>
+        </is>
       </c>
       <c r="CS78" t="inlineStr">
         <is>
@@ -77282,7 +77590,7 @@
       </c>
       <c r="AV79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW79" t="inlineStr">
@@ -77297,22 +77605,22 @@
       </c>
       <c r="AY79" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="BB79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC79" t="inlineStr">
@@ -77507,11 +77815,15 @@
           <t>26.85</t>
         </is>
       </c>
-      <c r="CQ79" t="n">
-        <v>27.29</v>
-      </c>
-      <c r="CR79" t="n">
-        <v>25.85</v>
+      <c r="CQ79" t="inlineStr">
+        <is>
+          <t>27.29</t>
+        </is>
+      </c>
+      <c r="CR79" t="inlineStr">
+        <is>
+          <t>25.85</t>
+        </is>
       </c>
       <c r="CS79" t="inlineStr">
         <is>
@@ -78264,7 +78576,7 @@
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
@@ -78279,22 +78591,22 @@
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
@@ -78489,11 +78801,15 @@
           <t>26.71</t>
         </is>
       </c>
-      <c r="CQ80" t="n">
-        <v>27.3</v>
-      </c>
-      <c r="CR80" t="n">
-        <v>25.81</v>
+      <c r="CQ80" t="inlineStr">
+        <is>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="CR80" t="inlineStr">
+        <is>
+          <t>25.81</t>
+        </is>
       </c>
       <c r="CS80" t="inlineStr">
         <is>
@@ -79246,7 +79562,7 @@
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
@@ -79261,22 +79577,22 @@
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.0</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
@@ -79471,11 +79787,15 @@
           <t>26.55</t>
         </is>
       </c>
-      <c r="CQ81" t="n">
-        <v>27.34</v>
-      </c>
-      <c r="CR81" t="n">
-        <v>25.76</v>
+      <c r="CQ81" t="inlineStr">
+        <is>
+          <t>27.34</t>
+        </is>
+      </c>
+      <c r="CR81" t="inlineStr">
+        <is>
+          <t>25.76</t>
+        </is>
       </c>
       <c r="CS81" t="inlineStr">
         <is>
@@ -80228,7 +80548,7 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
@@ -80243,22 +80563,22 @@
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
@@ -80453,11 +80773,15 @@
           <t>26.51</t>
         </is>
       </c>
-      <c r="CQ82" t="n">
-        <v>27.37</v>
-      </c>
-      <c r="CR82" t="n">
-        <v>25.67</v>
+      <c r="CQ82" t="inlineStr">
+        <is>
+          <t>27.37</t>
+        </is>
+      </c>
+      <c r="CR82" t="inlineStr">
+        <is>
+          <t>25.67</t>
+        </is>
       </c>
       <c r="CS82" t="inlineStr">
         <is>
@@ -81210,7 +81534,7 @@
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
@@ -81225,7 +81549,7 @@
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
@@ -81435,11 +81759,15 @@
           <t>16.85</t>
         </is>
       </c>
-      <c r="CQ83" t="n">
-        <v>17.39</v>
-      </c>
-      <c r="CR83" t="n">
-        <v>18.25</v>
+      <c r="CQ83" t="inlineStr">
+        <is>
+          <t>17.39</t>
+        </is>
+      </c>
+      <c r="CR83" t="inlineStr">
+        <is>
+          <t>18.25</t>
+        </is>
       </c>
       <c r="CS83" t="inlineStr">
         <is>
@@ -82192,7 +82520,7 @@
       </c>
       <c r="AV84" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW84" t="inlineStr">
@@ -82207,7 +82535,7 @@
       </c>
       <c r="AY84" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ84" t="inlineStr">
@@ -82417,11 +82745,15 @@
           <t>16.96</t>
         </is>
       </c>
-      <c r="CQ84" t="n">
-        <v>17.48</v>
-      </c>
-      <c r="CR84" t="n">
-        <v>18.3</v>
+      <c r="CQ84" t="inlineStr">
+        <is>
+          <t>17.48</t>
+        </is>
+      </c>
+      <c r="CR84" t="inlineStr">
+        <is>
+          <t>18.3</t>
+        </is>
       </c>
       <c r="CS84" t="inlineStr">
         <is>
@@ -83174,7 +83506,7 @@
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
@@ -83189,7 +83521,7 @@
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
@@ -83399,11 +83731,15 @@
           <t>17.055</t>
         </is>
       </c>
-      <c r="CQ85" t="n">
-        <v>17.56</v>
-      </c>
-      <c r="CR85" t="n">
-        <v>18.35</v>
+      <c r="CQ85" t="inlineStr">
+        <is>
+          <t>17.56</t>
+        </is>
+      </c>
+      <c r="CR85" t="inlineStr">
+        <is>
+          <t>18.35</t>
+        </is>
       </c>
       <c r="CS85" t="inlineStr">
         <is>
@@ -84156,7 +84492,7 @@
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
@@ -84171,7 +84507,7 @@
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
@@ -84186,7 +84522,7 @@
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
@@ -84381,11 +84717,15 @@
           <t>17.19</t>
         </is>
       </c>
-      <c r="CQ86" t="n">
-        <v>17.66</v>
-      </c>
-      <c r="CR86" t="n">
-        <v>18.39</v>
+      <c r="CQ86" t="inlineStr">
+        <is>
+          <t>17.66</t>
+        </is>
+      </c>
+      <c r="CR86" t="inlineStr">
+        <is>
+          <t>18.39</t>
+        </is>
       </c>
       <c r="CS86" t="inlineStr">
         <is>
@@ -85138,7 +85478,7 @@
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
@@ -85153,7 +85493,7 @@
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
@@ -85168,7 +85508,7 @@
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
@@ -85363,11 +85703,15 @@
           <t>17.355</t>
         </is>
       </c>
-      <c r="CQ87" t="n">
-        <v>17.77</v>
-      </c>
-      <c r="CR87" t="n">
-        <v>18.44</v>
+      <c r="CQ87" t="inlineStr">
+        <is>
+          <t>17.77</t>
+        </is>
+      </c>
+      <c r="CR87" t="inlineStr">
+        <is>
+          <t>18.44</t>
+        </is>
       </c>
       <c r="CS87" t="inlineStr">
         <is>
@@ -86120,7 +86464,7 @@
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
@@ -86135,7 +86479,7 @@
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
@@ -86150,7 +86494,7 @@
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
@@ -86345,11 +86689,15 @@
           <t>17.51</t>
         </is>
       </c>
-      <c r="CQ88" t="n">
-        <v>17.88</v>
-      </c>
-      <c r="CR88" t="n">
-        <v>18.49</v>
+      <c r="CQ88" t="inlineStr">
+        <is>
+          <t>17.88</t>
+        </is>
+      </c>
+      <c r="CR88" t="inlineStr">
+        <is>
+          <t>18.49</t>
+        </is>
       </c>
       <c r="CS88" t="inlineStr">
         <is>
@@ -87102,7 +87450,7 @@
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
@@ -87117,7 +87465,7 @@
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
@@ -87132,7 +87480,7 @@
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
@@ -87327,11 +87675,15 @@
           <t>17.615</t>
         </is>
       </c>
-      <c r="CQ89" t="n">
-        <v>17.98</v>
-      </c>
-      <c r="CR89" t="n">
-        <v>18.54</v>
+      <c r="CQ89" t="inlineStr">
+        <is>
+          <t>17.98</t>
+        </is>
+      </c>
+      <c r="CR89" t="inlineStr">
+        <is>
+          <t>18.54</t>
+        </is>
       </c>
       <c r="CS89" t="inlineStr">
         <is>
@@ -88084,7 +88436,7 @@
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
@@ -88099,7 +88451,7 @@
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
@@ -88114,7 +88466,7 @@
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
@@ -88309,11 +88661,15 @@
           <t>17.73</t>
         </is>
       </c>
-      <c r="CQ90" t="n">
-        <v>18.08</v>
-      </c>
-      <c r="CR90" t="n">
-        <v>18.58</v>
+      <c r="CQ90" t="inlineStr">
+        <is>
+          <t>18.08</t>
+        </is>
+      </c>
+      <c r="CR90" t="inlineStr">
+        <is>
+          <t>18.58</t>
+        </is>
       </c>
       <c r="CS90" t="inlineStr">
         <is>
@@ -89066,7 +89422,7 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
@@ -89081,7 +89437,7 @@
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
@@ -89096,7 +89452,7 @@
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
@@ -89291,11 +89647,15 @@
           <t>17.815</t>
         </is>
       </c>
-      <c r="CQ91" t="n">
-        <v>18.16</v>
-      </c>
-      <c r="CR91" t="n">
-        <v>18.62</v>
+      <c r="CQ91" t="inlineStr">
+        <is>
+          <t>18.16</t>
+        </is>
+      </c>
+      <c r="CR91" t="inlineStr">
+        <is>
+          <t>18.62</t>
+        </is>
       </c>
       <c r="CS91" t="inlineStr">
         <is>
@@ -90048,7 +90408,7 @@
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
@@ -90063,7 +90423,7 @@
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
@@ -90078,7 +90438,7 @@
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
@@ -90273,11 +90633,15 @@
           <t>29.995</t>
         </is>
       </c>
-      <c r="CQ92" t="n">
-        <v>30.3</v>
-      </c>
-      <c r="CR92" t="n">
-        <v>31.94</v>
+      <c r="CQ92" t="inlineStr">
+        <is>
+          <t>30.3</t>
+        </is>
+      </c>
+      <c r="CR92" t="inlineStr">
+        <is>
+          <t>31.94</t>
+        </is>
       </c>
       <c r="CS92" t="inlineStr">
         <is>
@@ -91030,7 +91394,7 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
@@ -91045,7 +91409,7 @@
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
@@ -91060,7 +91424,7 @@
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
@@ -91255,11 +91619,15 @@
           <t>30.05</t>
         </is>
       </c>
-      <c r="CQ93" t="n">
-        <v>30.42</v>
-      </c>
-      <c r="CR93" t="n">
-        <v>32.02</v>
+      <c r="CQ93" t="inlineStr">
+        <is>
+          <t>30.42</t>
+        </is>
+      </c>
+      <c r="CR93" t="inlineStr">
+        <is>
+          <t>32.02</t>
+        </is>
       </c>
       <c r="CS93" t="inlineStr">
         <is>
@@ -92012,7 +92380,7 @@
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
@@ -92027,7 +92395,7 @@
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
@@ -92042,7 +92410,7 @@
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
@@ -92237,11 +92605,15 @@
           <t>30.085</t>
         </is>
       </c>
-      <c r="CQ94" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="CR94" t="n">
-        <v>32.11</v>
+      <c r="CQ94" t="inlineStr">
+        <is>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="CR94" t="inlineStr">
+        <is>
+          <t>32.11</t>
+        </is>
       </c>
       <c r="CS94" t="inlineStr">
         <is>
@@ -92994,7 +93366,7 @@
       </c>
       <c r="AV95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW95" t="inlineStr">
@@ -93009,7 +93381,7 @@
       </c>
       <c r="AY95" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ95" t="inlineStr">
@@ -93024,7 +93396,7 @@
       </c>
       <c r="BB95" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC95" t="inlineStr">
@@ -93219,11 +93591,15 @@
           <t>30.11</t>
         </is>
       </c>
-      <c r="CQ95" t="n">
-        <v>30.57</v>
-      </c>
-      <c r="CR95" t="n">
-        <v>32.18</v>
+      <c r="CQ95" t="inlineStr">
+        <is>
+          <t>30.57</t>
+        </is>
+      </c>
+      <c r="CR95" t="inlineStr">
+        <is>
+          <t>32.18</t>
+        </is>
       </c>
       <c r="CS95" t="inlineStr">
         <is>
@@ -93976,7 +94352,7 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
@@ -93991,7 +94367,7 @@
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
@@ -94006,7 +94382,7 @@
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
@@ -94201,11 +94577,15 @@
           <t>30.15499999999999</t>
         </is>
       </c>
-      <c r="CQ96" t="n">
-        <v>30.67</v>
-      </c>
-      <c r="CR96" t="n">
-        <v>32.26</v>
+      <c r="CQ96" t="inlineStr">
+        <is>
+          <t>30.67</t>
+        </is>
+      </c>
+      <c r="CR96" t="inlineStr">
+        <is>
+          <t>32.26</t>
+        </is>
       </c>
       <c r="CS96" t="inlineStr">
         <is>
@@ -94958,7 +95338,7 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
@@ -94973,7 +95353,7 @@
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
@@ -94988,7 +95368,7 @@
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
@@ -95183,11 +95563,15 @@
           <t>30.21</t>
         </is>
       </c>
-      <c r="CQ97" t="n">
-        <v>30.82</v>
-      </c>
-      <c r="CR97" t="n">
-        <v>32.36</v>
+      <c r="CQ97" t="inlineStr">
+        <is>
+          <t>30.82</t>
+        </is>
+      </c>
+      <c r="CR97" t="inlineStr">
+        <is>
+          <t>32.36</t>
+        </is>
       </c>
       <c r="CS97" t="inlineStr">
         <is>
@@ -95940,7 +96324,7 @@
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
@@ -95955,7 +96339,7 @@
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
@@ -95970,7 +96354,7 @@
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
@@ -96165,11 +96549,15 @@
           <t>30.29</t>
         </is>
       </c>
-      <c r="CQ98" t="n">
-        <v>30.97</v>
-      </c>
-      <c r="CR98" t="n">
-        <v>32.44</v>
+      <c r="CQ98" t="inlineStr">
+        <is>
+          <t>30.97</t>
+        </is>
+      </c>
+      <c r="CR98" t="inlineStr">
+        <is>
+          <t>32.44</t>
+        </is>
       </c>
       <c r="CS98" t="inlineStr">
         <is>
@@ -96922,7 +97310,7 @@
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
@@ -96937,7 +97325,7 @@
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
@@ -96952,7 +97340,7 @@
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
@@ -97147,11 +97535,15 @@
           <t>30.36</t>
         </is>
       </c>
-      <c r="CQ99" t="n">
-        <v>31.13</v>
-      </c>
-      <c r="CR99" t="n">
-        <v>32.52</v>
+      <c r="CQ99" t="inlineStr">
+        <is>
+          <t>31.13</t>
+        </is>
+      </c>
+      <c r="CR99" t="inlineStr">
+        <is>
+          <t>32.52</t>
+        </is>
       </c>
       <c r="CS99" t="inlineStr">
         <is>
@@ -97904,7 +98296,7 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
@@ -97919,7 +98311,7 @@
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
@@ -97934,7 +98326,7 @@
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
@@ -98129,11 +98521,15 @@
           <t>30.42</t>
         </is>
       </c>
-      <c r="CQ100" t="n">
-        <v>31.28</v>
-      </c>
-      <c r="CR100" t="n">
-        <v>32.6</v>
+      <c r="CQ100" t="inlineStr">
+        <is>
+          <t>31.28</t>
+        </is>
+      </c>
+      <c r="CR100" t="inlineStr">
+        <is>
+          <t>32.6</t>
+        </is>
       </c>
       <c r="CS100" t="inlineStr">
         <is>
